--- a/output/roomself_excel/13304.xlsx
+++ b/output/roomself_excel/13304.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>372648</v>
+        <v>120830</v>
       </c>
       <c r="D2" t="n">
-        <v>9652</v>
+        <v>2876</v>
       </c>
       <c r="E2" t="n">
-        <v>1003</v>
+        <v>380</v>
       </c>
       <c r="F2" t="n">
-        <v>836</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>93177</v>
+        <v>159555</v>
       </c>
       <c r="D3" t="n">
-        <v>2472</v>
+        <v>3724</v>
       </c>
       <c r="E3" t="n">
-        <v>385</v>
+        <v>524</v>
       </c>
       <c r="F3" t="n">
-        <v>289</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>63488</v>
+        <v>93177</v>
       </c>
       <c r="D4" t="n">
-        <v>2356</v>
+        <v>2472</v>
       </c>
       <c r="E4" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F4" t="n">
-        <v>257</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>204408</v>
+        <v>105485</v>
       </c>
       <c r="D5" t="n">
-        <v>5592</v>
+        <v>2848</v>
       </c>
       <c r="E5" t="n">
-        <v>731</v>
+        <v>345</v>
       </c>
       <c r="F5" t="n">
-        <v>449</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>105485</v>
+        <v>50935</v>
       </c>
       <c r="D6" t="n">
-        <v>2848</v>
+        <v>1868</v>
       </c>
       <c r="E6" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50935</v>
+        <v>21275</v>
       </c>
       <c r="D7" t="n">
-        <v>1868</v>
+        <v>1200</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21275</v>
+        <v>55125</v>
       </c>
       <c r="D8" t="n">
-        <v>1200</v>
+        <v>1960</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>54852</v>
+        <v>204408</v>
       </c>
       <c r="D9" t="n">
-        <v>2948</v>
+        <v>5592</v>
       </c>
       <c r="E9" t="n">
-        <v>678</v>
+        <v>731</v>
       </c>
       <c r="F9" t="n">
-        <v>109</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>87846</v>
+        <v>92263</v>
       </c>
       <c r="D10" t="n">
-        <v>2420</v>
+        <v>3804</v>
       </c>
       <c r="E10" t="n">
-        <v>417</v>
+        <v>329</v>
       </c>
       <c r="F10" t="n">
-        <v>269</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>55125</v>
+        <v>87846</v>
       </c>
       <c r="D11" t="n">
-        <v>1960</v>
+        <v>2420</v>
       </c>
       <c r="E11" t="n">
-        <v>340</v>
+        <v>417</v>
       </c>
       <c r="F11" t="n">
-        <v>205</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>69456</v>
+        <v>125253</v>
       </c>
       <c r="D12" t="n">
-        <v>2164</v>
+        <v>2900</v>
       </c>
       <c r="E12" t="n">
-        <v>226</v>
+        <v>381</v>
       </c>
       <c r="F12" t="n">
-        <v>176</v>
+        <v>372</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>328582</v>
+        <v>63488</v>
       </c>
       <c r="D13" t="n">
-        <v>9436</v>
+        <v>2356</v>
       </c>
       <c r="E13" t="n">
-        <v>830</v>
+        <v>382</v>
       </c>
       <c r="F13" t="n">
-        <v>741</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20976</v>
+        <v>54852</v>
       </c>
       <c r="D14" t="n">
-        <v>1264</v>
+        <v>2948</v>
       </c>
       <c r="E14" t="n">
-        <v>466</v>
+        <v>678</v>
       </c>
       <c r="F14" t="n">
-        <v>360</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12499</v>
+        <v>69456</v>
       </c>
       <c r="D15" t="n">
-        <v>1016</v>
+        <v>2164</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16">
@@ -778,15 +778,81 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>203329</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6948</v>
+      </c>
+      <c r="E16" t="n">
+        <v>740</v>
+      </c>
+      <c r="F16" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>20976</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1264</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>12499</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>89540</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D19" t="n">
         <v>2448</v>
       </c>
-      <c r="E16" t="n">
-        <v>792</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="E19" t="n">
+        <v>420</v>
+      </c>
+      <c r="F19" t="n">
         <v>242</v>
       </c>
     </row>

--- a/output/roomself_excel/13304.xlsx
+++ b/output/roomself_excel/13304.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2876</v>
       </c>
-      <c r="E2" t="n">
-        <v>380</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>370</v>
+        <v>342</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>352</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3724</v>
       </c>
-      <c r="E3" t="n">
-        <v>524</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>361</v>
+        <v>472</v>
+      </c>
+      <c r="G3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>322</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2472</v>
       </c>
-      <c r="E4" t="n">
-        <v>385</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>289</v>
+        <v>261</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>357</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +609,20 @@
       <c r="D5" t="n">
         <v>2848</v>
       </c>
-      <c r="E5" t="n">
-        <v>345</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>132</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +639,12 @@
       <c r="D6" t="n">
         <v>1868</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +661,12 @@
       <c r="D7" t="n">
         <v>1200</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +683,27 @@
       <c r="D8" t="n">
         <v>1960</v>
       </c>
-      <c r="E8" t="n">
-        <v>340</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>205</v>
+        <v>175</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>315</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -629,11 +721,27 @@
       <c r="D9" t="n">
         <v>5592</v>
       </c>
-      <c r="E9" t="n">
-        <v>731</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>449</v>
+        <v>519</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>681</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +759,20 @@
       <c r="D10" t="n">
         <v>3804</v>
       </c>
-      <c r="E10" t="n">
-        <v>329</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="G10" t="n">
+        <v>28</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +789,27 @@
       <c r="D11" t="n">
         <v>2420</v>
       </c>
-      <c r="E11" t="n">
-        <v>417</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>269</v>
+        <v>484</v>
+      </c>
+      <c r="G11" t="n">
+        <v>27</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>363</v>
+      </c>
+      <c r="J11" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -695,11 +827,27 @@
       <c r="D12" t="n">
         <v>2900</v>
       </c>
-      <c r="E12" t="n">
-        <v>381</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>372</v>
+        <v>356</v>
+      </c>
+      <c r="G12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>342</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -717,11 +865,27 @@
       <c r="D13" t="n">
         <v>2356</v>
       </c>
-      <c r="E13" t="n">
-        <v>382</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>257</v>
+        <v>357</v>
+      </c>
+      <c r="G13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>232</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -739,11 +903,27 @@
       <c r="D14" t="n">
         <v>2948</v>
       </c>
-      <c r="E14" t="n">
-        <v>678</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>109</v>
+        <v>84</v>
+      </c>
+      <c r="G14" t="n">
+        <v>25</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>653</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -761,12 +941,20 @@
       <c r="D15" t="n">
         <v>2164</v>
       </c>
-      <c r="E15" t="n">
-        <v>226</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>176</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="G15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,11 +971,27 @@
       <c r="D16" t="n">
         <v>6948</v>
       </c>
-      <c r="E16" t="n">
-        <v>740</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>364</v>
+        <v>335</v>
+      </c>
+      <c r="G16" t="n">
+        <v>25</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>672</v>
+      </c>
+      <c r="J16" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -805,12 +1009,12 @@
       <c r="D17" t="n">
         <v>1264</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1031,12 @@
       <c r="D18" t="n">
         <v>1016</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,11 +1053,27 @@
       <c r="D19" t="n">
         <v>2448</v>
       </c>
-      <c r="E19" t="n">
-        <v>420</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>242</v>
+        <v>483</v>
+      </c>
+      <c r="G19" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>370</v>
+      </c>
+      <c r="J19" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
